--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_004/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_004/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -355,6 +360,21 @@
       </text>
     </comment>
     <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1306,17 +1326,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>APU Inlet S-Duct CFD V&amp;V (VVP-APU-DFI-011)</t>
+          <t>APU S-Duct Inlet CFD V&amp;V (VVP-APU-DFI-011)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>S-duct inlet CFD for circumferential distortion and total pressure recovery prediction at cruise and takeoff conditions (M0.3–0.6, α = −2° to +4°)</t>
+          <t>S-duct inlet CFD for circumferential distortion and total pressure recovery prediction at cruise and takeoff conditions</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Compressible steady RANS (k–ω SST) model of an APU S-duct inlet used to rank screen geometries and bleed schedules at pre-PDR stage. Key QoIs are DC60 at the Aerodynamic Interface Plane, total pressure recovery, and swirl intensity. Acceptance bands per SYS-APU-REQ-254: DC60 within ±0.02 absolute, recovery within ±1.5 points. Valid for M0.3–0.6, α = −2° to +4°, ReD ≈ (4–7)×10^6. Higher incidence or off-design yaw is outside the validated envelope.</t>
+          <t>RANS CFD model (SU2 v8.0.2, k-ω SST) of an S-duct inlet used to rank screen geometries and bleed schedules for pre-PDR decisions. Operating window: M0.3–0.6, α = −2° to +4°, ReD ≈ (4–7)×10^6. Key QoIs are DC60 at the Aerodynamic Interface Plane, total pressure recovery, and swirl intensity. Acceptance per SYS-APU-REQ-254: DC60 prediction within ±0.02 absolute, recovery within ±1.5 points.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1354,9 +1374,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (VVP-APU-DFI-011 Rev C memo, R. Chen to J. Morales, 2026-08-06)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1417,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1485,7 +1505,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>DC60 prediction within ±0.02 absolute and total pressure recovery within ±1.5 points relative to wind-tunnel measurements across the validated operating window</t>
+          <t>Top-level system requirement specifying acceptance bands for CFD predictions: DC60 within ±0.02 absolute and total pressure recovery within ±1.5 percentage points relative to experimental data; traceability maintained in DOORS.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1507,12 +1527,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>SU2 v8.0.2 compressible steady RANS k–ω SST model (sduct-aip v1.3)</t>
+          <t>SU2 v8.0.2 S-Duct RANS Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Compressible steady RANS with k–ω SST and γ–Reθ transition, second-order upwind/central discretisation, run in SU2 v8.0.2 (NASA fork hash 9c1f…) on three hybrid unstructured grids (7.1M/19.4M/52.6M cells)</t>
+          <t>Compressible steady RANS model with k-ω SST turbulence closure, γ–Reθ transition, porous-jump bleed/screen representation, and second-order upwind/central discretisation on hybrid unstructured grids up to 52.6M cells.</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1544,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Wind-tunnel campaigns WT-SD-A (M0.3) and WT-SD-B (M0.5); WT log 23-145</t>
+          <t>Wind-Tunnel Campaigns WT-SD-A and WT-SD-B</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>AIP 40-port total pressure rake, five-hole probe swirl surveys, and wall pressures from two wind-tunnel campaigns; measurement uncertainties: DC60 ±0.008, recovery ±0.4 pts, swirl ±0.7 deg; NIST-traceable calibrations</t>
+          <t>Experimental AIP 40-port total pressure rake, five-hole swirl probe, and wall pressure data at M0.3 (WT-SD-A) and M0.5 (WT-SD-B) from tunnel article 42-SD-3 Rev B; NIST-traceable calibrations; DC60 uncertainty ±0.008, recovery ±0.4 pts, swirl ±0.7 deg.</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1561,29 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Bleed-slot porous-jump coupon test data; inlet survey rake/cobra probe data (WT log 23-145)</t>
+          <t>Inlet Boundary Condition Survey (WT log 23-145)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Inlet total pressure, total temperature, and turbulence intensity profiles from rake/cobra surveys (combined standard uncertainty: Pt 0.35%, Tt 0.2 K, U 0.6%); porous coefficients with ±10% lab uncertainty used as model boundary conditions</t>
+          <t>Rake/cobra probe surveys providing inlet total pressure, total temperature, and turbulence intensity profiles; NIST-traceable; combined standard uncertainties: Pt ±0.35%, Tt ±0.2 K, U ±0.6%; porous coefficients ±10% from coupon tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>ANSYS CFX 2023R1 Cross-Solver Sanity Check</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Independent CFD solver (SST) used to repeat two baseline cases via CGNS mesh mapping and matched BCs; DC60 differences ≤0.009, recovery within 0.6 pts relative to SU2 baseline.</t>
         </is>
       </c>
     </row>
@@ -1983,7 +2020,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Wind-tunnel baseline comparison — M0.3 (WT-SD-A)</t>
+          <t>AIP Distortion and Recovery Comparison — M0.3 Baseline (WT-SD-A)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1998,12 +2035,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>CFD DC60, total pressure recovery, and swirl compared against AIP rake and five-hole probe data at M0.3 baseline screen configuration</t>
+          <t>CFD DC60 and total pressure recovery predictions compared against 40-port AIP rake and wall pressure data at M0.3, baseline screen configuration; tunnel Re matched within 2%.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>WT-SD-A experimental measurements</t>
+          <t>WT-SD-A experimental data, NIST-traceable instrumentation</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2013,12 +2050,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Measurement uncertainty (DC60 ±0.008, recovery ±0.4 pts, swirl ±0.7 deg) combined with GCI and LHS input propagation</t>
+          <t>Combined GCI and LHS input uncertainty propagation (120 samples); DC60 combined uncertainty ±0.016</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>DC60 error +0.011; recovery error −0.9 pts; swirl RMS error 0.9 deg</t>
+          <t>DC60 error +0.011 (within ±0.02 band); recovery error −0.9 pts (within ±1.5 pts band)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2030,7 +2067,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Wind-tunnel baseline comparison — M0.5 (WT-SD-B)</t>
+          <t>AIP Distortion and Recovery Comparison — M0.5 Baseline (WT-SD-B)</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2040,12 +2077,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>CFD DC60, total pressure recovery, and swirl compared against AIP rake and five-hole probe data at M0.5 baseline screen configuration</t>
+          <t>CFD DC60, total pressure recovery, and swirl intensity compared against AIP rake and five-hole probe data at M0.5, baseline screen; tunnel Re matched within 2%. LHS uncertainty propagation gave 95% bound DC60 = 0.292 ± 0.015.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>WT-SD-B experimental measurements</t>
+          <t>WT-SD-B experimental data, NIST-traceable instrumentation</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2055,12 +2092,12 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>LHS (120 samples) over inlet Tu ±20%, porous C2 ±10%, screen porosity ±3%; GCI combined in quadrature</t>
+          <t>LHS (120 samples) over inlet Tu (±20%), porous C2 (±10%), screen porosity (±3%); GCI combined in quadrature; 95% CI reported</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>DC60 error +0.017; recovery error −1.2 pts; 95% DC60 bound 0.292 ± 0.015; combined uncertainty ±0.016</t>
+          <t>DC60 error +0.017 (within ±0.02 band); recovery error −1.2 pts (within ±1.5 pts band); swirl RMS error 0.9 deg</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2072,7 +2109,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>AoA envelope sweep — α = −2° to +6°</t>
+          <t>Angle-of-Attack Sweep Validation (α = −2° to +6°)</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2082,12 +2119,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>DC60 bias evaluated across angle-of-attack sweep to define validated operating window; at α = +6° separation shifts upstream and DC60 error exceeds acceptance band</t>
+          <t>AoA sweep from −2° to +6° tested experimentally and computationally. DC60 bias within +0.02 up to α = +4°. At α = +6°, separation shifts upstream and DC60 error grows to +0.036, exceeding the acceptance band and flagged as outside current use window.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Wind-tunnel measurements across AoA sweep</t>
+          <t>WT experimental AoA sweep data</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2097,19 +2134,19 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>DC60 bias within +0.02 up to α = +4°; error grows to +0.036 at α = +6°</t>
+          <t>DC60 error ≤+0.02 for α ≤ +4°; error +0.036 at α = +6°</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Mesh convergence study (GCI)</t>
+          <t>Mesh Convergence Study (Grid Convergence Index)</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2119,12 +2156,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three-grid mesh refinement study on hybrid unstructured grids (7.1M, 19.4M, 52.6M cells); GCI and observed order of convergence computed for DC60 and recovery</t>
+          <t>Three-level unstructured hybrid grid refinement study (7.1M / 19.4M / 52.6M cells) on the S-duct domain. GCI computed for DC60 and recovery; observed order of accuracy determined by Richardson extrapolation.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation benchmark; observed order vs. theoretical order 2</t>
+          <t>Richardson extrapolation / GCI theory</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2134,12 +2171,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI), 95% confidence interval</t>
+          <t>Grid Convergence Index at 95% confidence interval</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>GCI on DC60 = 0.006 (fine grid, 95% CI); observed order p = 1.86 (recovery), 1.72 (DC60)</t>
+          <t>GCI(DC60) = 0.006 (fine grid, 95% CI); observed order p = 1.86 (recovery), 1.72 (DC60); wall y+ 0.8–1.2</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2151,7 +2188,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Cross-solver sanity check — ANSYS CFX 2023R1</t>
+          <t>Cross-Solver Sanity Check (SU2 vs. ANSYS CFX 2023R1)</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2161,12 +2198,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Two cases repeated in ANSYS CFX 2023R1 (SST) using CGNS-mapped meshes and matched BCs to verify solution independence from solver code</t>
+          <t>Two baseline cases (M0.3 and M0.5) repeated in ANSYS CFX 2023R1 with SST turbulence, CGNS-mapped meshes, and matched boundary conditions to verify solver-independence of key QoIs.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>SU2 v8.0.2 baseline results</t>
+          <t>ANSYS CFX 2023R1 results</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2176,7 +2213,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>DC60 difference ≤0.009; recovery difference within 0.6 pts</t>
+          <t>DC60 difference ≤0.009; recovery difference ≤0.6 pts</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2330,12 +2367,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Simulation software verified through testing and quality management processes</t>
+          <t>Simulation software must be verified for RANS/SST capability with documented code quality controls.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>SU2 v8.0.2 (NASA fork, tagged "Galileo", hash 9c1f…) passes 187/187 Jenkins CI unit tests; static analysis clean; IEEE-754 compliance verified. Apptainer image (cfd_env_2026.07.sif) locks the exact compute environment. Git repo tagged v1.3 with closed issue tracker for all PDR-blocking items. One-click replay script reproduces AIP pressure fields to machine epsilon against archive. Cross-solver check in ANSYS CFX 2023R1 provides additional code-independence evidence.</t>
+          <t>SU2 v8.0.2 (tag "Galileo", NASA fork hash 9c1f…) operates under continuous integration: 187/187 unit tests passing, static analysis clean, IEEE-754 compliance checked. No open solver bugs affecting RANS/SST. Environment fully captured in Apptainer image cfd_env_2026.07.sif; case setup scripted in Python; meshes via Pointwise 2023R2; Git repo tagged v1.3; issue tracker confirms all PDR-blocking items closed. Data archived on LUSTRE with hash verification. Cross-solver check with ANSYS CFX 2023R1 provides additional code independence evidence.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2364,12 +2401,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code correctly solves governing equations, demonstrated by benchmark or analytical comparison</t>
+          <t>Code must demonstrably solve governing equations correctly; benchmark and MMS evidence required.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>MMS on 3D Euler recovers observed order p = 1.98 (pressure) and 1.96 (velocity), consistent with theoretical second-order scheme. Turbulent channel benchmark matches Spalding law to within 1.5% at y+ = 30–200. No open solver bugs affecting RANS/SST in the deployed feature set.</t>
+          <t>MMS on 3D Euler equations recovers observed order p = 1.98 (pressure) and 1.96 (velocity). Turbulent channel flow benchmark matches Spalding law to within 1.5% at y+ = 30–200. Prior NAC S-duct study (TN-NAC-22-017) with PIV validation provides additional lineage. Cross-solver agreement with CFX within DC60 ≤0.009 further corroborates numerical correctness.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2398,12 +2435,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Spatial discretization shown to be adequate; discretization error quantified</t>
+          <t>Spatial discretization error on key QoIs must be quantified and shown to be small relative to acceptance bands.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-grid mesh refinement study (7.1M/19.4M/52.6M cells, hybrid unstructured); GCI on DC60 = 0.006 at 95% CI on fine grid; observed order p = 1.86/1.72 for recovery/DC60 near theoretical second-order. Wall y+ ≈ 0.8–1.2; prism layers in corner separation region maintain Δy+ &lt; 1. Grid stretching factor ±20% sensitivity: DC60 change ≤0.003.</t>
+          <t>Three-level grid refinement study: 7.1M / 19.4M / 52.6M cells. GCI(DC60) = 0.006 at 95% CI on fine grid; observed order p = 1.86 (recovery) and 1.72 (DC60), consistent with nominal second-order scheme. Wall y+ 0.8–1.2 maintained; corner separation region refined with prism layers (Δy+ &lt; 1). Grid stretching factor ±20% sensitivity moved DC60 by ≤0.003. Discretization uncertainty included in combined uncertainty budget (GCI ⊕ input = ±0.016 total).</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2432,12 +2469,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Iterative solver convergence demonstrated to be adequate</t>
+          <t>Iterative convergence must be demonstrated to negligible levels relative to discretization error.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals driven to 1e-6; mass imbalance &lt;0.05%; AIP probe monitors flat for last 3,000 iterations. Pseudo-time stepping reduced CFL from 50 to 5 before final Newton sweeps. DC60 repeatability across restarts within 0.002, confirming asymptotic convergence.</t>
+          <t>Residuals driven to 1×10^-6; mass imbalance &lt;0.05%; AIP probe monitors flat for last 3,000 iterations. CFL ramped from 50 to 5 before final Newton sweeps. DC60 repeatability across restarts within 0.002, well below the GCI of 0.006. Coupled pressure-velocity (RhoCentral preconditioned), double precision, segregated energy.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2466,12 +2503,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Model setup verified independently; boundary conditions and mesh quality checked</t>
+          <t>Model setup must be independently checked; boundary conditions and geometry must be verified against physical articles.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Case setup scripted in Python (reproducible, version-controlled). Independent reviewer A. Gupta (not on design team) performed mesh and BC audits and re-ran the M0.5 baseline from scratch, matching DC60 within 0.003. Geometry blockage verified to match tunnel insert within 0.3%. Activities executed per VVP-APU-DFI-011 Rev C with DOORS traceability to SYS-APU-REQ-254.</t>
+          <t>Independent reviewer A. Gupta (not on design team, 5-yr inlet CFD experience) performed mesh and BC audits and re-ran the M0.5 baseline from scratch, matching DC60 within 0.003. CAD from WT article 42-SD-3 Rev B; blockage matches tunnel insert to within 0.3%. WT trips and rake stems included in geometry. One-click replay script confirms full reproducibility (hash of AIP pressure field matches archive to machine epsilon). All activities traced in VVP-APU-DFI-011 Rev C; deviations (DES deferral) formally documented in VRR minutes 2026-06-28.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2500,12 +2537,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Mathematical model adequately represents the relevant physics; known limitations documented</t>
+          <t>Governing equations and turbulence model must be justified for the flow physics; known limitations must be documented.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Compressible steady RANS with k–ω SST selected; rationale supported by SST outperforming SA-BCM in DC60 accuracy across cases (SA-BCM cuts DC60 by 0.006, moving away from data). γ–Reθ transition model applied for clean-duct runs. Roughness sensitivity evaluated separately. Key limitations documented: model breaks down at α = +6° where separation shifts upstream; DES deferred (documented deviation in VRR minutes 2026-06-28); no heat soak; smooth walls only.</t>
+          <t>Compressible steady RANS with k-ω SST chosen; γ–Reθ transition used for clean-duct runs; SST shown to outperform SA-BCM (which reduced DC60 by 0.006 from data). Calorically perfect air assumption and smooth-wall idealisation documented as limitations. Roughness sensitivity quantified separately (+0.008 DC60 per +10 μm). DES branch deferred and flagged as next step. Separation at α = +6° identified as model-form limitation at off-design. Prior NAC S-duct PIV study provides physics-basis lineage.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2534,12 +2571,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Input data accurately characterised with uncertainty; boundary conditions from measurements</t>
+          <t>Boundary condition data must be traceable to calibrated measurements; input uncertainties must be characterised.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Inlet Pt, Tt, turbulence intensity from NIST-traceable rake/cobra probe surveys (WT log 23-145): combined standard uncertainty Pt 0.35%, Tt 0.2 K, U 0.6%. Porous-jump coefficients from coupon tests with ±10% lab uncertainty. Screen porosity from manufacturer data. CAD from WT article 42-SD-3 Rev B. Geometry includes wind-tunnel trips and rake stems. LHS propagation covers Tu ±20%, porous C2 ±10%, screen porosity ±3%.</t>
+          <t>Inlet Pt, Tt, and turbulence intensity from NIST-traceable rake/cobra probe surveys (WT log 23-145): combined standard uncertainties Pt ±0.35%, Tt ±0.2 K, U ±0.6%. Porous-jump coefficients from coupon tests with ±10% lab uncertainty. Screen porosity mapped from manufacturer data. Input uncertainties propagated through LHS (120 samples) over Tu (±20%), porous C2 (±10%), porosity (±3%). One-at-a-time sensitivity also documented (DC60 changes per parameter).</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2568,12 +2605,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Experimental test articles are adequate and representative</t>
+          <t>Experimental test articles must be adequately characterised and representative of the design intent.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Two wind-tunnel campaigns (WT-SD-A at M0.3, WT-SD-B at M0.5) conducted on article 42-SD-3 Rev B, which includes trips and rake stems matched in the CFD geometry. Tunnel Re matched to within 2% of target. Prior NAC S-duct study (TN-NAC-22-017) with PIV validation provides additional lineage evidence. Number of replicate specimens or statistical sample size characterisation not explicitly stated.</t>
+          <t>Single wind-tunnel article (42-SD-3 Rev B) used for both WT-SD-A (M0.3) and WT-SD-B (M0.5) campaigns. Geometry blockage matches CFD domain to within 0.3%. WT trips and rake stems explicitly represented in the model. No explicit statistical characterisation of multiple articles or production-representativeness stated; evidence is adequate for pre-PDR decisions but not final certification.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2602,12 +2639,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions well-controlled and measured with quantified uncertainty</t>
+          <t>Test conditions must be well-controlled with calibrated instrumentation; measurement uncertainties must be quantified.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>AIP 40-port total pressure rake, five-hole probes (swirl), and wall pressures used. Calibrations NIST-traceable. Measurement uncertainties reported: DC60 ±0.008, recovery ±0.4 pts, swirl ±0.7 deg, inlet Pt 0.35%, Tt 0.2 K, U 0.6%. Overall tunnel Re matched within 2%. AoA sweep from −2° to +6° tested.</t>
+          <t>NIST-traceable calibrations for all instrumentation. Tunnel Reynolds number matched within 2% of CFD target. AIP 40-port total pressure rake, five-hole probes (swirl), and wall pressures employed. Quantified data uncertainties: DC60 ±0.008, recovery ±0.4 pts, swirl ±0.7 deg. AoA sweep from −2° to +6° tested. Inlet survey uncertainties (Pt, Tt, U) NIST-traceable per WT log 23-145.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2636,12 +2673,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs match experimental conditions with propagated uncertainty</t>
+          <t>CFD boundary conditions must match experimental test conditions with uncertainties propagated.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Inlet profiles (Pt, Tt, Tu) from the same rake surveys (WT log 23-145) used to set CFD boundary conditions. Geometry includes tunnel-specific features (trips, rake stems); blockage matches tunnel insert to within 0.3%. Porous coefficients derived from coupon tests match tunnel screen hardware. One-at-a-time sensitivity analysis quantifies DC60 response to input parameter variations (Tu, C2, roughness). LHS propagation provides combined input uncertainty bound.</t>
+          <t>Inlet profiles (Pt, Tt, Tu) extracted directly from WT survey (WT log 23-145) and applied as CFD boundary conditions. Blockage agreement within 0.3%. Tunnel Re matched within 2%. Porous coefficients derived from same test article's coupon data. Input parameter comparison is explicit; LHS propagation quantifies impact of residual mismatches (±0.015 DC60 at 95% CI at M0.5). One-at-a-time sensitivity provides traceability for each input contribution.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2670,12 +2707,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Model predictions compared to experimental data with quantitative metrics and uncertainty bands</t>
+          <t>CFD predictions must be quantitatively compared to experimental data for all key QoIs with uncertainty bands; errors must be within acceptance bands.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative errors reported for DC60 (+0.011 at M0.3, +0.017 at M0.5), recovery (−0.9, −1.2 pts), and swirl RMS (0.9 deg) against experimental data with stated measurement uncertainties. All errors within acceptance band (±0.02 DC60, ±1.5 pts recovery) for the validated window. Combined uncertainty (GCI ⊕ input UQ) ±0.016 at M0.5 baseline meets acceptance band. AoA envelope shows bias exceedance at α = +6° flagged explicitly. Cross-solver check provides additional comparison point.</t>
+          <t>Quantitative comparison for DC60, recovery, and swirl at M0.3 and M0.5: DC60 errors +0.011 / +0.017 (band ±0.02); recovery errors −0.9 / −1.2 pts (band ±1.5); swirl RMS 0.9 deg. Combined uncertainty ±0.016 meets acceptance band. AoA sweep provides multiple comparison points; off-design failure at α = +6° (error +0.036) explicitly documented. Cross-solver comparison and sensitivity checks supplement the primary comparison.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2704,12 +2741,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly measure the safety/performance concern and are measurable computationally and experimentally</t>
+          <t>Model QoIs must directly address the engineering decision (screen geometry and bleed sizing) and be measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>DC60 at AIP, total pressure recovery, and swirl intensity are the standard aerodynamic interface quantities governing APU inlet screen design and bleed sizing decisions. All three QoIs are directly measurable in both CFD (AIP probe monitors) and experiment (40-port rake, five-hole probes) using the same spatial definition. Traceability to SYS-APU-REQ-254 in DOORS confirmed.</t>
+          <t>DC60, total pressure recovery, and swirl intensity are the canonical AIP distortion descriptors required by SYS-APU-REQ-254 for APU screen and bleed design trades. All three QoIs are measured by the experimental instrumentation (40-port rake, five-hole probes, wall pressures) and computed directly from CFD post-processing. Traceability from QoIs to requirement maintained in DOORS.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2738,12 +2775,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions match the intended operating conditions, geometry, and physics regime</t>
+          <t>Validation conditions must cover the intended operating envelope; gaps must be documented.</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation campaigns (M0.3, M0.5) directly bracket the COU flight envelope (M0.3–0.6). Same geometry (article 42-SD-3 Rev B) and same screen/bleed configurations used in both experiment and CFD. Re matched within 2%. AoA range −2° to +4° validated; COU limited to this window. Gaps: M0.6 upper boundary not explicitly validated (M0.5 is highest tested); α = +6° outside window with documented error growth; roughness (service life) and off-design yaw not fully covered; DES deferred. These gaps are explicitly documented and the COU is bounded accordingly.</t>
+          <t>Validation covers M0.3 and M0.5 within the stated COU window (M0.3–0.6) and AoA −2° to +4°. Same geometry (42-SD-3 Rev B), same physics regime (compressible RANS, similar Re). Identified gaps: M0.6 not explicitly validated (M0.5 is the upper validated point); α = +5° and +6° show growing error and are explicitly excluded from COU. Yaw off-design not yet validated; roughness effects not incorporated in primary runs. Prior NAC study (TN-NAC-22-017, M0.2–0.6 with PIV) provides partial additional coverage. DES pilot deferred; proposed for downselect phase.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2928,7 +2965,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Within the stated operating window (M0.3–0.6, α = −2° to +4°, ReD ≈ (4–7)×10^6), all DC60 and recovery prediction errors are within the SYS-APU-REQ-254 acceptance bands (±0.02 DC60, ±1.5 pts recovery). Combined uncertainty (GCI ⊕ LHS input propagation) of ±0.016 also meets the band. Code verification, mesh convergence, solver convergence, independent review, and NIST-traceable experimental data collectively support adequate credibility for pre-PDR screen and bleed sizing trades. Acceptance is conditional on restricting use to the validated envelope: α ≤ +4°, M ≤ 0.6, smooth walls, no significant yaw. For α = +6°, significant surface roughness, or off-design yaw, outputs are trend-only pending DES validation and additional wind-tunnel data at expanded conditions (as documented in VRR minutes 2026-06-28 and the proposed next-steps plan).</t>
+          <t>Within the stated operating window (M0.3–0.6, α = −2° to +4°, ReD ≈ (4–7)×10^6), the SU2 RANS/SST S-duct inlet model meets all acceptance criteria of SYS-APU-REQ-254: DC60 errors of +0.011 and +0.017 (both within ±0.02), recovery errors of −0.9 and −1.2 pts (both within ±1.5 pts), combined uncertainty ±0.016 within the band, and GCI(DC60) = 0.006. Independent review by A. Gupta confirmed reproducibility. The model is accepted for pre-PDR screen geometry and bleed-sizing trade studies within the validated envelope. Conditions on acceptance: (1) outputs at α &gt; +4° or significant surface roughness (service life) must be treated as trend-only and paired with targeted tunnel data or DES before hardware commitment; (2) M0.6 and yaw off-design cases require validation expansion before use at those conditions; (3) the deferred DES branch should be pursued at downselect as documented in VRR minutes 2026-06-28.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
